--- a/data/trans_orig/P70D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63710</t>
+          <t>65045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78404</t>
+          <t>78616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154805</t>
+          <t>155279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169005</t>
+          <t>168966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>30251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329149</t>
+          <t>328685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345590</t>
+          <t>345621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334579</t>
+          <t>335049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349144</t>
+          <t>349579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669239</t>
+          <t>671808</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>692047</t>
+          <t>692191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>27995</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>19859</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>39890</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27995</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19338</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>38941</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440216</t>
+          <t>440121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455518</t>
+          <t>455634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329619</t>
+          <t>330652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>342629</t>
+          <t>342718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,47 +1579,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>786383</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>774488</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>794519</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>97,56%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>786383</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>775437</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>795040</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>43426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>78666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>702071</t>
+          <t>703101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>738695</t>
+          <t>739330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>406603</t>
+          <t>405094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>434553</t>
+          <t>434122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1123982</t>
+          <t>1121844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1173372</t>
+          <t>1173478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36188</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59137</t>
+          <t>58736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>262457</t>
+          <t>262809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281146</t>
+          <t>280792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177861</t>
+          <t>178127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191298</t>
+          <t>191058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446553</t>
+          <t>446954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>469502</t>
+          <t>468850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -2788,97 +2788,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -2901,97 +2901,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49777</t>
+          <t>50276</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96815</t>
+          <t>101240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67339</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108218</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125685</t>
+          <t>124570</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196400</t>
+          <t>192169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1870167</t>
+          <t>1865742</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1917205</t>
+          <t>1916706</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1355425</t>
+          <t>1358225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1396304</t>
+          <t>1397985</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3234226</t>
+          <t>3238457</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3304941</t>
+          <t>3306056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Edad-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>82401</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65045</t>
+          <t>73033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>164124</t>
+          <t>187222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155279</t>
+          <t>177189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>168966</t>
+          <t>193083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>21606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>340011</t>
+          <t>383964</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328685</t>
+          <t>373011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345621</t>
+          <t>389925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>343796</t>
+          <t>308019</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335049</t>
+          <t>298666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349579</t>
+          <t>313707</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>683807</t>
+          <t>691984</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671808</t>
+          <t>677941</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>692191</t>
+          <t>700420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>394617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>394617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>394617</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>702059</t>
+          <t>713822</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>702059</t>
+          <t>713822</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>702059</t>
+          <t>713822</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>30047</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>42416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>448918</t>
+          <t>524375</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440121</t>
+          <t>514742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455634</t>
+          <t>531071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>337465</t>
+          <t>382626</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330652</t>
+          <t>374530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>342718</t>
+          <t>388599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>786383</t>
+          <t>907002</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>774488</t>
+          <t>894633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794519</t>
+          <t>915871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>463168</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>463168</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>463168</t>
+          <t>539458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>351210</t>
+          <t>397591</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>351210</t>
+          <t>397591</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351210</t>
+          <t>397591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>814378</t>
+          <t>937049</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>814378</t>
+          <t>937049</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>814378</t>
+          <t>937049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43426</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48889</t>
+          <t>38832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54811</t>
+          <t>55591</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>70147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>720770</t>
+          <t>517688</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>703101</t>
+          <t>505273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>739330</t>
+          <t>526404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>424928</t>
+          <t>426913</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>405094</t>
+          <t>416607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>434122</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1145699</t>
+          <t>944601</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1121844</t>
+          <t>930045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1173478</t>
+          <t>956994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>746527</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>746527</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>746527</t>
+          <t>544753</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>453983</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>453983</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>453983</t>
+          <t>455439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1000192</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1000192</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1000192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36177</t>
+          <t>39854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>30720</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58736</t>
+          <t>64085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>273241</t>
+          <t>299816</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>262809</t>
+          <t>288048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280792</t>
+          <t>308480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>185100</t>
+          <t>208605</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178127</t>
+          <t>200947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191058</t>
+          <t>214895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>458340</t>
+          <t>508422</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446954</t>
+          <t>495484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>468850</t>
+          <t>519632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>327902</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>327902</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>298986</t>
+          <t>327902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206705</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>505690</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>505690</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>505690</t>
+          <t>559569</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16581</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>33426</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32397</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>67463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>104557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>108319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124570</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192169</t>
+          <t>202238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1890078</t>
+          <t>1849495</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1865742</t>
+          <t>1827977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1916706</t>
+          <t>1865071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1379863</t>
+          <t>1424976</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1358225</t>
+          <t>1406377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1397985</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3269942</t>
+          <t>3274471</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3238457</t>
+          <t>3244992</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3306056</t>
+          <t>3297373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1966982</t>
+          <t>1932534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1463643</t>
+          <t>1514696</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3430626</t>
+          <t>3447230</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
